--- a/data/trending_integrated_20261019_13.xlsx
+++ b/data/trending_integrated_20261019_13.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F2" t="n">
         <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20493132212</v>
+        <v>20502085468</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 공급 단독 뉴스 확인. 외인 매수세 유입되며 전고점 돌파 기대.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 공급 계약 체결. 외인 매수세 유입에 따른 상승 기대감 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '강관 공급', '외인 매집']</t>
+          <t>['KBI동양철관', '스페이스X', '강관 공급']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,21 +659,21 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9450</v>
+        <v>9420</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.83%</t>
+          <t>'+11.48%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F3" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3" t="n">
         <v>206</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>22793939530</v>
+        <v>22937495100</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -747,184 +747,184 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9240</v>
+        <v>170500</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.55%</t>
+          <t>'+1.97%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.02</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>61</v>
       </c>
       <c r="F4" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="H4" t="n">
-        <v>1.74</v>
+        <v>75.02</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9010</v>
+        <v>167200</v>
       </c>
       <c r="K4" t="n">
-        <v>8810</v>
+        <v>159600</v>
       </c>
       <c r="L4" t="n">
-        <v>9500</v>
+        <v>175500</v>
       </c>
       <c r="M4" t="n">
-        <v>8510</v>
+        <v>159200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.72</v>
+        <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>129481615480</v>
+        <v>474710673000</v>
       </c>
       <c r="P4" t="n">
-        <v>9500</v>
+        <v>243500</v>
       </c>
       <c r="Q4" t="n">
-        <v>2270</v>
+        <v>71000</v>
       </c>
       <c r="R4" t="n">
-        <v>-181000</v>
+        <v>59000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-30000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HT로보틱스, 시장 전반의 어려움 속에서 로봇주 긍정적 언급 있으나, 분석글 후 급락 가능성 및 개인 투자자 손실 경험 공유.</t>
+          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['로봇주', '급락', '손실']</t>
+          <t>['우선주', '주문실수', '외인매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>171100</v>
+        <v>9180</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+2.33%</t>
+          <t>'+1.89%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
-        <v>61</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="G5" t="n">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="H5" t="n">
-        <v>75.02</v>
+        <v>1.74</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>167200</v>
+        <v>9010</v>
       </c>
       <c r="K5" t="n">
-        <v>159600</v>
+        <v>8810</v>
       </c>
       <c r="L5" t="n">
-        <v>175500</v>
+        <v>9500</v>
       </c>
       <c r="M5" t="n">
-        <v>159200</v>
+        <v>8510</v>
       </c>
       <c r="N5" t="n">
-        <v>75</v>
+        <v>0.72</v>
       </c>
       <c r="O5" t="n">
-        <v>466302337100</v>
+        <v>132960468765</v>
       </c>
       <c r="P5" t="n">
-        <v>243500</v>
+        <v>9500</v>
       </c>
       <c r="Q5" t="n">
-        <v>71000</v>
+        <v>2270</v>
       </c>
       <c r="R5" t="n">
-        <v>59000</v>
+        <v>-181000</v>
       </c>
       <c r="S5" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
+          <t>HT로보틱스, 로봇주 전반의 강세 속 소폭 상승. 투자 경고 종목 지정 가능성 언급. 명확한 호재 및 악재 분석 부족.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['우선주', '주문실수', '외인매수']</t>
+          <t>['HT로보틱스', '로봇주', '투자 경고']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14950</v>
+        <v>14920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.49%</t>
+          <t>'+1.29%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F6" t="n">
         <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="H6" t="n">
         <v>9.699999999999999</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>27271766795</v>
+        <v>27645409025</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, '이재명 대통령' 언급하며 주가 조작 및 뱅크런 관련 의혹 제기. 외인 보유율 관련 주장도 존재하나 근거 부족.</t>
+          <t>대우건설, 이재명 대통령 관련 부정적 언급 다수. 주가 조작 및 뱅크런 의혹 제기. 명확한 팩트 기반 분석 부재.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['이재명', '주가 조작', '뱅크런']</t>
+          <t>['대우건설', '이재명', '주가 조작']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>217500</v>
+        <v>216500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.93%</t>
+          <t>'+0.46%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="G7" t="n">
-        <v>1606</v>
+        <v>1642</v>
       </c>
       <c r="H7" t="n">
         <v>45.99</v>
@@ -1070,7 +1070,7 @@
         <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>2104404934500</v>
+        <v>2149770682000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자, 바닥 다지기 후 상승 서킷 기대감. 그러나 이재명 관련 정치적 언급 및 연기금 이탈 언급 존재.</t>
+          <t>삼성전자, 국내 증시 전반의 악재 반영 완료 및 바닥 다지기 구간 진입 분석. 일부 기대감 존재하나 뚜렷한 근거 부족.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['바닥 다지기', '이재명', '연기금']</t>
+          <t>['삼성전자', '바닥 다지기', '악재 반영']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1263000</v>
+        <v>1259000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.71%</t>
+          <t>'-1.02%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="G8" t="n">
-        <v>1699</v>
+        <v>1683</v>
       </c>
       <c r="H8" t="n">
         <v>48.82</v>
@@ -1162,7 +1162,7 @@
         <v>48.85</v>
       </c>
       <c r="O8" t="n">
-        <v>2773041138500</v>
+        <v>2835416285000</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 상장 관련 금융감독원 중복 상장 우려 및 최태원 관련 논란 부각. 주주 속았다는 부정적 의견 다수.</t>
+          <t>SK하이닉스, 솔리다임 상장 관련 금융감독원의 중복 상장 우려 전달. 상장 철회 가능성 제기되며 주주 불안감 증폭.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복 상장', '최태원']</t>
+          <t>['SK하이닉스', '솔리다임', '중복 상장']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1228,7 +1228,7 @@
         <v>36</v>
       </c>
       <c r="G9" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H9" t="n">
         <v>0.06</v>
@@ -1254,7 +1254,7 @@
         <v>0.11</v>
       </c>
       <c r="O9" t="n">
-        <v>27680876605</v>
+        <v>27795878075</v>
       </c>
       <c r="P9" t="n">
         <v>30800</v>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18070</v>
+        <v>18040</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.79%</t>
+          <t>'-1.96%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10" t="n">
         <v>205</v>
@@ -1337,7 +1337,7 @@
         <v>17690</v>
       </c>
       <c r="L10" t="n">
-        <v>18080</v>
+        <v>18110</v>
       </c>
       <c r="M10" t="n">
         <v>17670</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>32672710685</v>
+        <v>33798346745</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14150</v>
+        <v>14070</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.73%</t>
+          <t>'-6.26%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F11" t="n">
         <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>39049641190</v>
+        <v>39373139300</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.30%</t>
+          <t>'-7.14%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
         <v>74</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>11561379565</v>
+        <v>11720128187</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>

--- a/data/trending_integrated_20261019_13.xlsx
+++ b/data/trending_integrated_20261019_13.xlsx
@@ -584,7 +584,7 @@
         <v>71</v>
       </c>
       <c r="G2" t="n">
-        <v>541</v>
+        <v>571</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20502085468</v>
+        <v>20511921464</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 공급 계약 체결. 외인 매수세 유입에 따른 상승 기대감 형성.</t>
+          <t>스페이스X 로켓 발사대 강관 공급 계약 뉴스 기반으로 주가 상승 기대감 형성. 외인 매집 정황 포착.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['KBI동양철관', '스페이스X', '강관 공급']</t>
+          <t>['KBI동양철관', '스페이스X', '강관']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F3" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>22937495100</v>
+        <v>23232813520</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -711,14 +711,14 @@
         <v>5390</v>
       </c>
       <c r="R3" t="n">
-        <v>-259000</v>
+        <v>-211000</v>
       </c>
       <c r="S3" t="n">
         <v>5000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>테슬라 로드스터 관련 수혜주로 언급되며, 자사주 매입 호재가 있으나 공매도와 프로그램 매도에 대한 경계도 존재함.</t>
+          <t>테슬라 로드스터 수혜주로 언급되며, 전체 매출의 70% 테슬라 납품 사실 기반 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['테슬라', '로드스터', '자사주 매입']</t>
+          <t>['명신산업', '테슬라', '로드스터']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,184 +747,184 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170500</v>
+        <v>9190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.97%</t>
+          <t>'+2.00%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E4" t="n">
+        <v>119</v>
+      </c>
+      <c r="F4" t="n">
         <v>61</v>
       </c>
-      <c r="F4" t="n">
-        <v>50</v>
-      </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="H4" t="n">
-        <v>75.02</v>
+        <v>1.74</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>167200</v>
+        <v>9010</v>
       </c>
       <c r="K4" t="n">
-        <v>159600</v>
+        <v>8810</v>
       </c>
       <c r="L4" t="n">
-        <v>175500</v>
+        <v>9500</v>
       </c>
       <c r="M4" t="n">
-        <v>159200</v>
+        <v>8510</v>
       </c>
       <c r="N4" t="n">
-        <v>75</v>
+        <v>0.72</v>
       </c>
       <c r="O4" t="n">
-        <v>474710673000</v>
+        <v>139282708735</v>
       </c>
       <c r="P4" t="n">
-        <v>243500</v>
+        <v>9500</v>
       </c>
       <c r="Q4" t="n">
-        <v>71000</v>
+        <v>2270</v>
       </c>
       <c r="R4" t="n">
-        <v>59000</v>
+        <v>-230000</v>
       </c>
       <c r="S4" t="n">
-        <v>-30000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
+          <t>단일가 지정예고 및 투자경고 관련 언급. 시장 전반적인 하락세 속에서 투자자들의 불확실성 표출.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['우선주', '주문실수', '외인매수']</t>
+          <t>['HT로보틱스', '단일가', '투자경고']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9180</v>
+        <v>169700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.89%</t>
+          <t>'+1.50%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74</v>
+        <v>75.02</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9010</v>
+        <v>167200</v>
       </c>
       <c r="K5" t="n">
-        <v>8810</v>
+        <v>159600</v>
       </c>
       <c r="L5" t="n">
-        <v>9500</v>
+        <v>175500</v>
       </c>
       <c r="M5" t="n">
-        <v>8510</v>
+        <v>159200</v>
       </c>
       <c r="N5" t="n">
-        <v>0.72</v>
+        <v>75</v>
       </c>
       <c r="O5" t="n">
-        <v>132960468765</v>
+        <v>486324691950</v>
       </c>
       <c r="P5" t="n">
-        <v>9500</v>
+        <v>243500</v>
       </c>
       <c r="Q5" t="n">
-        <v>2270</v>
+        <v>71000</v>
       </c>
       <c r="R5" t="n">
-        <v>-181000</v>
+        <v>-73000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-23000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HT로보틱스, 로봇주 전반의 강세 속 소폭 상승. 투자 경고 종목 지정 가능성 언급. 명확한 호재 및 악재 분석 부족.</t>
+          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['HT로보틱스', '로봇주', '투자 경고']</t>
+          <t>['우선주', '주문실수', '외인매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14920</v>
+        <v>14890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.29%</t>
+          <t>'+1.09%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="F6" t="n">
         <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="H6" t="n">
         <v>9.699999999999999</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>27645409025</v>
+        <v>28335558120</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -987,23 +987,23 @@
         <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>32000</v>
+        <v>-91000</v>
       </c>
       <c r="S6" t="n">
-        <v>-29000</v>
+        <v>-79000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 이재명 대통령 관련 부정적 언급 다수. 주가 조작 및 뱅크런 의혹 제기. 명확한 팩트 기반 분석 부재.</t>
+          <t>주가조작 및 뱅크런 관련 의혹 제기. 특정 정치인 언급하며 비판적인 논조 유지.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['대우건설', '이재명', '주가 조작']</t>
+          <t>['대우건설', '주가조작', '뱅크런']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>216500</v>
+        <v>215750</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.46%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="G7" t="n">
-        <v>1642</v>
+        <v>1614</v>
       </c>
       <c r="H7" t="n">
         <v>45.99</v>
@@ -1070,7 +1070,7 @@
         <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>2149770682000</v>
+        <v>2212003132000</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1079,23 +1079,23 @@
         <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>1715000</v>
+        <v>1544000</v>
       </c>
       <c r="S7" t="n">
-        <v>573000</v>
+        <v>729000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>삼성전자, 국내 증시 전반의 악재 반영 완료 및 바닥 다지기 구간 진입 분석. 일부 기대감 존재하나 뚜렷한 근거 부족.</t>
+          <t>시장 악재 반영 완료 및 바닥 다지기 구간 진입 예상. 일부에서는 외인 및 연기금 수급 불안정 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['삼성전자', '바닥 다지기', '악재 반영']</t>
+          <t>['삼성전자', '반도체', 'AI']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1259000</v>
+        <v>1256000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.02%</t>
+          <t>'-1.26%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,7 +1136,7 @@
         <v>495</v>
       </c>
       <c r="G8" t="n">
-        <v>1683</v>
+        <v>1609</v>
       </c>
       <c r="H8" t="n">
         <v>48.82</v>
@@ -1162,7 +1162,7 @@
         <v>48.85</v>
       </c>
       <c r="O8" t="n">
-        <v>2835416285000</v>
+        <v>2898881478500</v>
       </c>
       <c r="P8" t="n">
         <v>2987000</v>
@@ -1171,23 +1171,23 @@
         <v>465500</v>
       </c>
       <c r="R8" t="n">
-        <v>54000</v>
+        <v>-13000</v>
       </c>
       <c r="S8" t="n">
-        <v>59000</v>
+        <v>52000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 상장 관련 금융감독원의 중복 상장 우려 전달. 상장 철회 가능성 제기되며 주주 불안감 증폭.</t>
+          <t>솔리다임 중복상장 관련 금감원 우려 표명으로 상장 철회 가능성 대두. 주주들은 최태원 회장 관련 불만 제기.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '솔리다임', '중복 상장']</t>
+          <t>['SK하이닉스', '솔리다임', '중복상장']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14770</v>
+        <v>14760</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.20%</t>
+          <t>'-1.27%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.05</v>
       </c>
       <c r="E9" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
         <v>83</v>
@@ -1254,7 +1254,7 @@
         <v>0.11</v>
       </c>
       <c r="O9" t="n">
-        <v>27795878075</v>
+        <v>27882923085</v>
       </c>
       <c r="P9" t="n">
         <v>30800</v>
@@ -1263,7 +1263,7 @@
         <v>9810</v>
       </c>
       <c r="R9" t="n">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="S9" t="n">
         <v>1000</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18040</v>
+        <v>18030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.96%</t>
+          <t>'-2.01%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>0.08</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F10" t="n">
         <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>33798346745</v>
+        <v>35020943195</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1355,10 +1355,10 @@
         <v>17210</v>
       </c>
       <c r="R10" t="n">
-        <v>-481000</v>
+        <v>-602000</v>
       </c>
       <c r="S10" t="n">
-        <v>4000</v>
+        <v>-28000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14070</v>
+        <v>13990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.26%</t>
+          <t>'-6.80%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G11" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>39373139300</v>
+        <v>39824492725</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1447,7 +1447,7 @@
         <v>13610</v>
       </c>
       <c r="R11" t="n">
-        <v>35000</v>
+        <v>32000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1487,11 +1487,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.14%</t>
+          <t>'-7.22%</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1504,7 +1504,7 @@
         <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>11720128187</v>
+        <v>11775577825</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>
@@ -1539,7 +1539,7 @@
         <v>192</v>
       </c>
       <c r="R12" t="n">
-        <v>-321000</v>
+        <v>-343000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>

--- a/data/trending_integrated_20261019_13.xlsx
+++ b/data/trending_integrated_20261019_13.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F2" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20511921464</v>
+        <v>20531555000</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9420</v>
+        <v>9540</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.48%</t>
+          <t>'+12.90%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>23232813520</v>
+        <v>23603070680</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>테슬라 로드스터 수혜주로 언급되며, 전체 매출의 70% 테슬라 납품 사실 기반 주가 상승 기대.</t>
+          <t>테슬라 로드스터 수혜주로 인한 11000원 돌파 기대감. 저평가 해소를 위한 수급 기대와 공매도 관련 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['명신산업', '테슬라', '로드스터']</t>
+          <t>['테슬라', '로드스터', '수혜주']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,184 +747,184 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9190</v>
+        <v>170300</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+2.00%</t>
+          <t>'+1.85%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.02</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="G4" t="n">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="H4" t="n">
-        <v>1.74</v>
+        <v>75.02</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9010</v>
+        <v>167200</v>
       </c>
       <c r="K4" t="n">
-        <v>8810</v>
+        <v>159600</v>
       </c>
       <c r="L4" t="n">
-        <v>9500</v>
+        <v>175500</v>
       </c>
       <c r="M4" t="n">
-        <v>8510</v>
+        <v>159200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.72</v>
+        <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>139282708735</v>
+        <v>494446656750</v>
       </c>
       <c r="P4" t="n">
-        <v>9500</v>
+        <v>243500</v>
       </c>
       <c r="Q4" t="n">
-        <v>2270</v>
+        <v>71000</v>
       </c>
       <c r="R4" t="n">
-        <v>-230000</v>
+        <v>-73000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-23000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>단일가 지정예고 및 투자경고 관련 언급. 시장 전반적인 하락세 속에서 투자자들의 불확실성 표출.</t>
+          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['HT로보틱스', '단일가', '투자경고']</t>
+          <t>['우선주', '주문실수', '외인매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>169700</v>
+        <v>9140</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.50%</t>
+          <t>'+1.44%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
+        <v>116</v>
+      </c>
+      <c r="F5" t="n">
         <v>61</v>
       </c>
-      <c r="F5" t="n">
-        <v>49</v>
-      </c>
       <c r="G5" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H5" t="n">
-        <v>75.02</v>
+        <v>1.74</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>167200</v>
+        <v>9010</v>
       </c>
       <c r="K5" t="n">
-        <v>159600</v>
+        <v>8810</v>
       </c>
       <c r="L5" t="n">
-        <v>175500</v>
+        <v>9500</v>
       </c>
       <c r="M5" t="n">
-        <v>159200</v>
+        <v>8510</v>
       </c>
       <c r="N5" t="n">
-        <v>75</v>
+        <v>0.72</v>
       </c>
       <c r="O5" t="n">
-        <v>486324691950</v>
+        <v>141135799995</v>
       </c>
       <c r="P5" t="n">
-        <v>243500</v>
+        <v>9500</v>
       </c>
       <c r="Q5" t="n">
-        <v>71000</v>
+        <v>2270</v>
       </c>
       <c r="R5" t="n">
-        <v>-73000</v>
+        <v>-230000</v>
       </c>
       <c r="S5" t="n">
-        <v>-23000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
+          <t xml:space="preserve">로봇주로서의 긍정적인 시장 전망과 함께 단기 과열 및 투자 경고 가능성 언급. 개인 투자자들의 수익 실현 및 관망세. </t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['우선주', '주문실수', '외인매수']</t>
+          <t>['로봇주', '단기과열', '투자경고']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14890</v>
+        <v>14860</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+1.09%</t>
+          <t>'+0.88%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F6" t="n">
         <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="H6" t="n">
         <v>9.699999999999999</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>28335558120</v>
+        <v>28982639155</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가조작 및 뱅크런 관련 의혹 제기. 특정 정치인 언급하며 비판적인 논조 유지.</t>
+          <t>주가 조작 및 뱅크런 관련 의혹 제기로 인한 부정적 전망. 외인 보유율 조절 및 주주 행동 촉구.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['대우건설', '주가조작', '뱅크런']</t>
+          <t>['주가조작', '뱅크런', '외인보유율']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,11 +1027,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>215750</v>
+        <v>216000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1041,10 +1041,10 @@
         <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="G7" t="n">
-        <v>1614</v>
+        <v>1637</v>
       </c>
       <c r="H7" t="n">
         <v>45.99</v>
@@ -1070,7 +1070,7 @@
         <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>2212003132000</v>
+        <v>2282375275500</v>
       </c>
       <c r="P7" t="n">
         <v>374500</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>시장 악재 반영 완료 및 바닥 다지기 구간 진입 예상. 일부에서는 외인 및 연기금 수급 불안정 언급.</t>
+          <t>세상 악재 반영 및 바닥 다지기 완료 후 상승 기대감. 외인 매수세 유입 가능성과 연기금 매도세 혼재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['삼성전자', '반도체', 'AI']</t>
+          <t>['악재', '바닥다지기', '외인매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,184 +1115,184 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1256000</v>
+        <v>14940</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.26%</t>
+          <t>'-0.07%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>61</v>
       </c>
       <c r="F8" t="n">
-        <v>495</v>
+        <v>35</v>
       </c>
       <c r="G8" t="n">
-        <v>1609</v>
+        <v>93</v>
       </c>
       <c r="H8" t="n">
-        <v>48.82</v>
+        <v>0.06</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>1272000</v>
+        <v>14950</v>
       </c>
       <c r="K8" t="n">
-        <v>1212000</v>
+        <v>14610</v>
       </c>
       <c r="L8" t="n">
-        <v>1268000</v>
+        <v>16600</v>
       </c>
       <c r="M8" t="n">
-        <v>1208000</v>
+        <v>14610</v>
       </c>
       <c r="N8" t="n">
-        <v>48.85</v>
+        <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>2898881478500</v>
+        <v>28117702005</v>
       </c>
       <c r="P8" t="n">
-        <v>2987000</v>
+        <v>30800</v>
       </c>
       <c r="Q8" t="n">
-        <v>465500</v>
+        <v>9810</v>
       </c>
       <c r="R8" t="n">
-        <v>-13000</v>
+        <v>20000</v>
       </c>
       <c r="S8" t="n">
-        <v>52000</v>
+        <v>1000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>솔리다임 중복상장 관련 금감원 우려 표명으로 상장 철회 가능성 대두. 주주들은 최태원 회장 관련 불만 제기.</t>
+          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '솔리다임', '중복상장']</t>
+          <t>['하이드로겔', '주문폭증', '신규주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14760</v>
+        <v>1261000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.27%</t>
+          <t>'-0.86%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>485</v>
       </c>
       <c r="G9" t="n">
-        <v>83</v>
+        <v>1588</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06</v>
+        <v>48.82</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>14950</v>
+        <v>1272000</v>
       </c>
       <c r="K9" t="n">
-        <v>14610</v>
+        <v>1212000</v>
       </c>
       <c r="L9" t="n">
-        <v>16600</v>
+        <v>1268000</v>
       </c>
       <c r="M9" t="n">
-        <v>14610</v>
+        <v>1208000</v>
       </c>
       <c r="N9" t="n">
-        <v>0.11</v>
+        <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>27882923085</v>
+        <v>2966886761500</v>
       </c>
       <c r="P9" t="n">
-        <v>30800</v>
+        <v>2987000</v>
       </c>
       <c r="Q9" t="n">
-        <v>9810</v>
+        <v>465500</v>
       </c>
       <c r="R9" t="n">
-        <v>20000</v>
+        <v>-13000</v>
       </c>
       <c r="S9" t="n">
-        <v>1000</v>
+        <v>52000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
+          <t>솔리다임 상장 중복 상장 저촉 판단으로 인한 상장 철회 가능성 부각. 긍정적인 호재로 작용하며 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['하이드로겔', '주문폭증', '신규주']</t>
+          <t>['솔리다임', '중복상장', '공시']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18030</v>
+        <v>18010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.01%</t>
+          <t>'-2.12%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>35020943195</v>
+        <v>35688472855</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,21 +1395,21 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13990</v>
+        <v>13970</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.80%</t>
+          <t>'-6.93%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11" t="n">
         <v>102</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>39824492725</v>
+        <v>40283001540</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.22%</t>
+          <t>'-7.61%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
         <v>77</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>11775577825</v>
+        <v>11839290051</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>

--- a/data/trending_integrated_20261019_13.xlsx
+++ b/data/trending_integrated_20261019_13.xlsx
@@ -584,7 +584,7 @@
         <v>72</v>
       </c>
       <c r="G2" t="n">
-        <v>579</v>
+        <v>584</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20531555000</v>
+        <v>20539366812</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>스페이스X 로켓 발사대 강관 공급 계약 뉴스 기반으로 주가 상승 기대감 형성. 외인 매집 정황 포착.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 950톤 공급 사실 확인. 외인 매수세 유입되며 전고점 돌파 기대감 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['KBI동양철관', '스페이스X', '강관']</t>
+          <t>['스페이스X', '강관', '납품']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9540</v>
+        <v>9510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.90%</t>
+          <t>'+12.54%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>65</v>
       </c>
       <c r="G3" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>23603070680</v>
+        <v>24171065280</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -747,103 +747,103 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170300</v>
+        <v>9150</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.85%</t>
+          <t>'+1.55%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E4" t="n">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="F4" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="G4" t="n">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H4" t="n">
-        <v>75.02</v>
+        <v>1.74</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>167200</v>
+        <v>9010</v>
       </c>
       <c r="K4" t="n">
-        <v>159600</v>
+        <v>8810</v>
       </c>
       <c r="L4" t="n">
-        <v>175500</v>
+        <v>9500</v>
       </c>
       <c r="M4" t="n">
-        <v>159200</v>
+        <v>8510</v>
       </c>
       <c r="N4" t="n">
-        <v>75</v>
+        <v>0.72</v>
       </c>
       <c r="O4" t="n">
-        <v>494446656750</v>
+        <v>141808421235</v>
       </c>
       <c r="P4" t="n">
-        <v>243500</v>
+        <v>9500</v>
       </c>
       <c r="Q4" t="n">
-        <v>71000</v>
+        <v>2270</v>
       </c>
       <c r="R4" t="n">
-        <v>-73000</v>
+        <v>-230000</v>
       </c>
       <c r="S4" t="n">
-        <v>-23000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
+          <t>HT로보틱스, 단기과열 및 투자경고 지정 예고. 분석글 게시 후 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['우선주', '주문실수', '외인매수']</t>
+          <t>['단기과열', '투자경고', '급락']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9140</v>
+        <v>169600</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -851,80 +851,80 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>116</v>
+        <v>63</v>
       </c>
       <c r="F5" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74</v>
+        <v>75.02</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9010</v>
+        <v>167200</v>
       </c>
       <c r="K5" t="n">
-        <v>8810</v>
+        <v>159600</v>
       </c>
       <c r="L5" t="n">
-        <v>9500</v>
+        <v>175500</v>
       </c>
       <c r="M5" t="n">
-        <v>8510</v>
+        <v>159200</v>
       </c>
       <c r="N5" t="n">
-        <v>0.72</v>
+        <v>75</v>
       </c>
       <c r="O5" t="n">
-        <v>141135799995</v>
+        <v>503953544900</v>
       </c>
       <c r="P5" t="n">
-        <v>9500</v>
+        <v>243500</v>
       </c>
       <c r="Q5" t="n">
-        <v>2270</v>
+        <v>71000</v>
       </c>
       <c r="R5" t="n">
-        <v>-230000</v>
+        <v>-73000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-23000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t xml:space="preserve">로봇주로서의 긍정적인 시장 전망과 함께 단기 과열 및 투자 경고 가능성 언급. 개인 투자자들의 수익 실현 및 관망세. </t>
+          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['로봇주', '단기과열', '투자경고']</t>
+          <t>['우선주', '주문실수', '외인매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14860</v>
+        <v>14790</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.88%</t>
+          <t>'+0.41%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" t="n">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="H6" t="n">
         <v>9.699999999999999</v>
@@ -978,7 +978,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>28982639155</v>
+        <v>29526211195</v>
       </c>
       <c r="P6" t="n">
         <v>40350</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>주가 조작 및 뱅크런 관련 의혹 제기로 인한 부정적 전망. 외인 보유율 조절 및 주주 행동 촉구.</t>
+          <t>대우건설, 정치적 이슈 언급 다수. 주가 조작 및 뱅크런 관련 부정적 논조.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가조작', '뱅크런', '외인보유율']</t>
+          <t>['주가 조작', '뱅크런', '정치']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,184 +1023,184 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>216000</v>
+        <v>15000</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.33%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
-        <v>506</v>
+        <v>35</v>
       </c>
       <c r="G7" t="n">
-        <v>1637</v>
+        <v>87</v>
       </c>
       <c r="H7" t="n">
-        <v>45.99</v>
+        <v>0.06</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>215500</v>
+        <v>14950</v>
       </c>
       <c r="K7" t="n">
-        <v>207000</v>
+        <v>14610</v>
       </c>
       <c r="L7" t="n">
-        <v>219500</v>
+        <v>16600</v>
       </c>
       <c r="M7" t="n">
-        <v>206500</v>
+        <v>14610</v>
       </c>
       <c r="N7" t="n">
-        <v>45.98</v>
+        <v>0.11</v>
       </c>
       <c r="O7" t="n">
-        <v>2282375275500</v>
+        <v>28463957090</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>30800</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>9810</v>
       </c>
       <c r="R7" t="n">
-        <v>1544000</v>
+        <v>20000</v>
       </c>
       <c r="S7" t="n">
-        <v>729000</v>
+        <v>1000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>세상 악재 반영 및 바닥 다지기 완료 후 상승 기대감. 외인 매수세 유입 가능성과 연기금 매도세 혼재.</t>
+          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['악재', '바닥다지기', '외인매수']</t>
+          <t>['하이드로겔', '주문폭증', '신규주']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14940</v>
+        <v>215750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'+0.12%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>61</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>35</v>
+        <v>503</v>
       </c>
       <c r="G8" t="n">
-        <v>93</v>
+        <v>1698</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06</v>
+        <v>45.99</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14950</v>
+        <v>215500</v>
       </c>
       <c r="K8" t="n">
-        <v>14610</v>
+        <v>207000</v>
       </c>
       <c r="L8" t="n">
-        <v>16600</v>
+        <v>219500</v>
       </c>
       <c r="M8" t="n">
-        <v>14610</v>
+        <v>206500</v>
       </c>
       <c r="N8" t="n">
-        <v>0.11</v>
+        <v>45.98</v>
       </c>
       <c r="O8" t="n">
-        <v>28117702005</v>
+        <v>2321399377500</v>
       </c>
       <c r="P8" t="n">
-        <v>30800</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>9810</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>20000</v>
+        <v>1544000</v>
       </c>
       <c r="S8" t="n">
-        <v>1000</v>
+        <v>729000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
+          <t>삼성전자, 외국인 매수세 1위 기록. 주주환원 시작 및 연간 영업이익, 배당율 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['하이드로겔', '주문폭증', '신규주']</t>
+          <t>['외국인', '매수', '주주환원']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1261000</v>
+        <v>1258000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.86%</t>
+          <t>'-1.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="G9" t="n">
-        <v>1588</v>
+        <v>1604</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>2966886761500</v>
+        <v>3026197830500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 상장 중복 상장 저촉 판단으로 인한 상장 철회 가능성 부각. 긍정적인 호재로 작용하며 주가 상승 기대.</t>
+          <t>SK하이닉스, 솔리다임 중복상장 우려 제기. 금감원, 중복상장 저촉 판단하며 상장 철회 가능성 높아짐.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복상장', '공시']</t>
+          <t>['솔리다임', '중복상장', '금감원']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18010</v>
+        <v>17990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.12%</t>
+          <t>'-2.23%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>35688472855</v>
+        <v>36336041305</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13970</v>
+        <v>14180</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.93%</t>
+          <t>'-5.53%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F11" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>40283001540</v>
+        <v>41361245800</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.61%</t>
+          <t>'-7.77%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>11839290051</v>
+        <v>11966144733</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>

--- a/data/trending_integrated_20261019_13.xlsx
+++ b/data/trending_integrated_20261019_13.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G2" t="n">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20539366812</v>
+        <v>20575181584</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9510</v>
+        <v>9500</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+12.54%</t>
+          <t>'+12.43%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F3" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G3" t="n">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>24171065280</v>
+        <v>24360236420</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>테슬라 로드스터 수혜주로 인한 11000원 돌파 기대감. 저평가 해소를 위한 수급 기대와 공매도 관련 언급.</t>
+          <t>테슬라 로드스터 수혜주 및 전체 매출 70% 테슬라 납품. 저평가주 수급 기대.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['테슬라', '로드스터', '수혜주']</t>
+          <t>['테슬라', '로드스터', '납품']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -747,254 +747,254 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9150</v>
+        <v>170200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.55%</t>
+          <t>'+1.79%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.02</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="H4" t="n">
-        <v>1.74</v>
+        <v>75.02</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9010</v>
+        <v>167200</v>
       </c>
       <c r="K4" t="n">
-        <v>8810</v>
+        <v>159600</v>
       </c>
       <c r="L4" t="n">
-        <v>9500</v>
+        <v>175500</v>
       </c>
       <c r="M4" t="n">
-        <v>8510</v>
+        <v>159200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.72</v>
+        <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>141808421235</v>
+        <v>510911688550</v>
       </c>
       <c r="P4" t="n">
-        <v>9500</v>
+        <v>243500</v>
       </c>
       <c r="Q4" t="n">
-        <v>2270</v>
+        <v>71000</v>
       </c>
       <c r="R4" t="n">
-        <v>-230000</v>
+        <v>-73000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-23000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>HT로보틱스, 단기과열 및 투자경고 지정 예고. 분석글 게시 후 급락 가능성 언급.</t>
+          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['단기과열', '투자경고', '급락']</t>
+          <t>['우선주', '주문실수', '외인매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>169600</v>
+        <v>9120</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+1.44%</t>
+          <t>'+1.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="G5" t="n">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="H5" t="n">
-        <v>75.02</v>
+        <v>1.74</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>167200</v>
+        <v>9010</v>
       </c>
       <c r="K5" t="n">
-        <v>159600</v>
+        <v>8810</v>
       </c>
       <c r="L5" t="n">
-        <v>175500</v>
+        <v>9500</v>
       </c>
       <c r="M5" t="n">
-        <v>159200</v>
+        <v>8510</v>
       </c>
       <c r="N5" t="n">
-        <v>75</v>
+        <v>0.72</v>
       </c>
       <c r="O5" t="n">
-        <v>503953544900</v>
+        <v>142523230715</v>
       </c>
       <c r="P5" t="n">
-        <v>243500</v>
+        <v>9500</v>
       </c>
       <c r="Q5" t="n">
-        <v>71000</v>
+        <v>2270</v>
       </c>
       <c r="R5" t="n">
-        <v>-73000</v>
+        <v>-230000</v>
       </c>
       <c r="S5" t="n">
-        <v>-23000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
+          <t>HT로보틱스, 단기과열 및 투자경고 지정 예고. 분석글 게시 후 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['우선주', '주문실수', '외인매수']</t>
+          <t>['단기과열', '투자경고', '급락']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14790</v>
+        <v>15000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.41%</t>
+          <t>'+0.33%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>127</v>
+        <v>61</v>
       </c>
       <c r="F6" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>234</v>
+        <v>89</v>
       </c>
       <c r="H6" t="n">
-        <v>9.699999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14730</v>
+        <v>14950</v>
       </c>
       <c r="K6" t="n">
-        <v>14500</v>
+        <v>14610</v>
       </c>
       <c r="L6" t="n">
-        <v>15070</v>
+        <v>16600</v>
       </c>
       <c r="M6" t="n">
-        <v>14120</v>
+        <v>14610</v>
       </c>
       <c r="N6" t="n">
-        <v>9.779999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="O6" t="n">
-        <v>29526211195</v>
+        <v>28608148155</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>30800</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>9810</v>
       </c>
       <c r="R6" t="n">
-        <v>-91000</v>
+        <v>20000</v>
       </c>
       <c r="S6" t="n">
-        <v>-79000</v>
+        <v>1000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 정치적 이슈 언급 다수. 주가 조작 및 뱅크런 관련 부정적 논조.</t>
+          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,112 +1003,112 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가 조작', '뱅크런', '정치']</t>
+          <t>['하이드로겔', '주문폭증', '신규주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15000</v>
+        <v>14770</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'+0.27%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>132</v>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>87</v>
+        <v>282</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14950</v>
+        <v>14730</v>
       </c>
       <c r="K7" t="n">
-        <v>14610</v>
+        <v>14500</v>
       </c>
       <c r="L7" t="n">
-        <v>16600</v>
+        <v>15070</v>
       </c>
       <c r="M7" t="n">
-        <v>14610</v>
+        <v>14120</v>
       </c>
       <c r="N7" t="n">
-        <v>0.11</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>28463957090</v>
+        <v>29969839340</v>
       </c>
       <c r="P7" t="n">
-        <v>30800</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>9810</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>20000</v>
+        <v>-91000</v>
       </c>
       <c r="S7" t="n">
-        <v>1000</v>
+        <v>-79000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
+          <t>주가 조작 의혹 및 외인보유율 관련 논란.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['하이드로겔', '주문폭증', '신규주']</t>
+          <t>['주가조작', '외인보유율', '논란']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>215750</v>
+        <v>216000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.12%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1133,10 +1133,10 @@
         <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="G8" t="n">
-        <v>1698</v>
+        <v>1701</v>
       </c>
       <c r="H8" t="n">
         <v>45.99</v>
@@ -1162,7 +1162,7 @@
         <v>45.98</v>
       </c>
       <c r="O8" t="n">
-        <v>2321399377500</v>
+        <v>2369046758500</v>
       </c>
       <c r="P8" t="n">
         <v>374500</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자, 외국인 매수세 1위 기록. 주주환원 시작 및 연간 영업이익, 배당율 언급.</t>
+          <t>19일 외국인 순매수 1위 기록. 주주환원 시작 및 바닥 다짐 전망.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외국인', '매수', '주주환원']</t>
+          <t>['외국인', '순매수', '주주환원']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="G9" t="n">
-        <v>1604</v>
+        <v>1681</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>3026197830500</v>
+        <v>3088782684500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임 중복상장 우려 제기. 금감원, 중복상장 저촉 판단하며 상장 철회 가능성 높아짐.</t>
+          <t>솔리다임 중복상장 제동 관련 금융감독원 판단. 상장 철회 가능성 부각.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17990</v>
+        <v>18010</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.23%</t>
+          <t>'-2.12%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>36336041305</v>
+        <v>37013735690</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14180</v>
+        <v>14160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.53%</t>
+          <t>'-5.66%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F11" t="n">
         <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>41361245800</v>
+        <v>41571496570</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.77%</t>
+          <t>'-8.09%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>11966144733</v>
+        <v>12015635734</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>
